--- a/scores_9klasses_new/tables/az_ids.xlsx
+++ b/scores_9klasses_new/tables/az_ids.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administarator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\analytics\scores_9klasses_new\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13BC115B-17B5-4FB6-B4A1-23318DA9753F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FD24C1-DFC8-4BB9-B1B3-BA5ADF2C7D61}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Результат запроса" sheetId="1" r:id="rId1"/>
@@ -8948,5 +8948,6 @@
     <sortCondition descending="1" ref="C2:C777"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>